--- a/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20261021.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20261021.xlsx
@@ -887,17 +887,17 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>168,000</t>
+          <t>556,404</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
@@ -909,17 +909,17 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>556,404</t>
+          <t>168,000</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
@@ -1151,17 +1151,17 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>3189</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>景碩</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>449,000</t>
+          <t>591,000</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -1173,17 +1173,17 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>3189</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>景碩</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>591,000</t>
+          <t>449,000</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -1327,17 +1327,17 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>健鼎</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>6,456,000</t>
+          <t>745,000</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -1349,17 +1349,17 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>健鼎</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>745,000</t>
+          <t>6,456,000</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -1415,17 +1415,17 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>技嘉</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>3,380,000</t>
+          <t>957,659</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -1437,17 +1437,17 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>技嘉</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>957,659</t>
+          <t>3,380,000</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -1635,17 +1635,17 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>6805</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>45,000</t>
+          <t>95,000</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
@@ -1657,17 +1657,17 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>6805</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>95,000</t>
+          <t>45,000</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
@@ -1701,17 +1701,17 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>2377</t>
+          <t>6257</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>微星</t>
+          <t>矽格</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>1,212,076</t>
+          <t>793,000</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -1723,17 +1723,17 @@
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>6257</t>
+          <t>2377</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>矽格</t>
+          <t>微星</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>793,000</t>
+          <t>1,212,076</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
@@ -1877,17 +1877,17 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>2474</t>
+          <t>6531</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>可成</t>
+          <t>愛普*</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>775,000</t>
+          <t>186,000</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
@@ -1921,17 +1921,17 @@
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>6531</t>
+          <t>2474</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>愛普*</t>
+          <t>可成</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>186,000</t>
+          <t>775,000</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
@@ -1987,17 +1987,17 @@
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>339,000</t>
+          <t>118,000</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
@@ -2009,17 +2009,17 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>3006</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>晶豪科</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>424,000</t>
+          <t>174,000</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
@@ -2031,17 +2031,17 @@
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>118,000</t>
+          <t>65,538</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
@@ -2053,17 +2053,17 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>174,000</t>
+          <t>339,000</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
@@ -2075,17 +2075,17 @@
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>3006</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>晶豪科</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>65,538</t>
+          <t>424,000</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
@@ -2119,17 +2119,17 @@
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>2467</t>
+          <t>3005</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>志聖</t>
+          <t>神基</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>160,000</t>
+          <t>695,000</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
@@ -2141,17 +2141,17 @@
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>3005</t>
+          <t>2467</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>神基</t>
+          <t>志聖</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>695,000</t>
+          <t>160,000</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
@@ -2163,17 +2163,17 @@
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>3030</t>
+          <t>6526</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>德律</t>
+          <t>達發</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>260,000</t>
+          <t>73,000</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
@@ -2185,17 +2185,17 @@
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>6526</t>
+          <t>3030</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>達發</t>
+          <t>德律</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>73,000</t>
+          <t>260,000</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
